--- a/BI/TP_BI/D002.xlsx
+++ b/BI/TP_BI/D002.xlsx
@@ -1,15 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_95EB923B4EED9EE34FF2A19D72D1D1AE2B85D82C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -187,9 +201,9 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="172" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -233,7 +247,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -252,9 +266,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -292,9 +306,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -329,7 +343,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -364,7 +378,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -537,7 +551,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L391"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -624,9 +638,9 @@
       <c r="K2" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="2" t="e">
+      <c r="L2" s="2">
         <f ca="1">(RAND()*("14/01/2016"-"14/01/2010"+1))+"14/01/2010"</f>
-        <v>#VALUE!</v>
+        <v>40551.46043864901</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -663,9 +677,9 @@
       <c r="K3" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="2" t="e">
+      <c r="L3" s="2">
         <f t="shared" ref="L3:L66" ca="1" si="0">(RAND()*("14/01/2016"-"14/01/2010"+1))+"14/01/2010"</f>
-        <v>#VALUE!</v>
+        <v>41806.794540716437</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -702,9 +716,9 @@
       <c r="K4" t="s">
         <v>20</v>
       </c>
-      <c r="L4" s="2" t="e">
+      <c r="L4" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42155.421144960113</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
@@ -741,9 +755,9 @@
       <c r="K5" t="s">
         <v>23</v>
       </c>
-      <c r="L5" s="2" t="e">
+      <c r="L5" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40954.274715589163</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
@@ -780,9 +794,9 @@
       <c r="K6" t="s">
         <v>14</v>
       </c>
-      <c r="L6" s="2" t="e">
+      <c r="L6" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41617.445500989088</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
@@ -819,9 +833,9 @@
       <c r="K7" t="s">
         <v>23</v>
       </c>
-      <c r="L7" s="2" t="e">
+      <c r="L7" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41853.903241185049</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
@@ -858,9 +872,9 @@
       <c r="K8" t="s">
         <v>20</v>
       </c>
-      <c r="L8" s="2" t="e">
+      <c r="L8" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40536.28029826226</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
@@ -897,9 +911,9 @@
       <c r="K9" t="s">
         <v>20</v>
       </c>
-      <c r="L9" s="2" t="e">
+      <c r="L9" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42104.053255654035</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
@@ -936,9 +950,9 @@
       <c r="K10" t="s">
         <v>29</v>
       </c>
-      <c r="L10" s="2" t="e">
+      <c r="L10" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41405.154254784597</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
@@ -975,9 +989,9 @@
       <c r="K11" t="s">
         <v>29</v>
       </c>
-      <c r="L11" s="2" t="e">
+      <c r="L11" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42034.393723354726</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
@@ -1014,9 +1028,9 @@
       <c r="K12" t="s">
         <v>32</v>
       </c>
-      <c r="L12" s="2" t="e">
+      <c r="L12" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40677.528021192629</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1053,9 +1067,9 @@
       <c r="K13" t="s">
         <v>32</v>
       </c>
-      <c r="L13" s="2" t="e">
+      <c r="L13" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40357.5049985062</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1092,9 +1106,9 @@
       <c r="K14" t="s">
         <v>35</v>
       </c>
-      <c r="L14" s="2" t="e">
+      <c r="L14" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42365.110629050767</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
@@ -1131,9 +1145,9 @@
       <c r="K15" t="s">
         <v>37</v>
       </c>
-      <c r="L15" s="2" t="e">
+      <c r="L15" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41570.826607007257</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -1170,9 +1184,9 @@
       <c r="K16" t="s">
         <v>20</v>
       </c>
-      <c r="L16" s="2" t="e">
+      <c r="L16" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40670.657272459423</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
@@ -1209,9 +1223,9 @@
       <c r="K17" t="s">
         <v>23</v>
       </c>
-      <c r="L17" s="2" t="e">
+      <c r="L17" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42060.159005523165</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
@@ -1248,9 +1262,9 @@
       <c r="K18" t="s">
         <v>14</v>
       </c>
-      <c r="L18" s="2" t="e">
+      <c r="L18" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41274.277214952301</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
@@ -1287,9 +1301,9 @@
       <c r="K19" t="s">
         <v>32</v>
       </c>
-      <c r="L19" s="2" t="e">
+      <c r="L19" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41064.836632568346</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
@@ -1326,9 +1340,9 @@
       <c r="K20" t="s">
         <v>32</v>
       </c>
-      <c r="L20" s="2" t="e">
+      <c r="L20" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41361.334812393528</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
@@ -1365,9 +1379,9 @@
       <c r="K21" t="s">
         <v>43</v>
       </c>
-      <c r="L21" s="2" t="e">
+      <c r="L21" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41710.54271581467</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
@@ -1404,9 +1418,9 @@
       <c r="K22" t="s">
         <v>17</v>
       </c>
-      <c r="L22" s="2" t="e">
+      <c r="L22" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40194.112744429935</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
@@ -1443,9 +1457,9 @@
       <c r="K23" t="s">
         <v>17</v>
       </c>
-      <c r="L23" s="2" t="e">
+      <c r="L23" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40836.428227836906</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
@@ -1482,9 +1496,9 @@
       <c r="K24" t="s">
         <v>29</v>
       </c>
-      <c r="L24" s="2" t="e">
+      <c r="L24" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41006.642811233745</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
@@ -1521,9 +1535,9 @@
       <c r="K25" t="s">
         <v>17</v>
       </c>
-      <c r="L25" s="2" t="e">
+      <c r="L25" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42092.310824420143</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
@@ -1560,9 +1574,9 @@
       <c r="K26" t="s">
         <v>14</v>
       </c>
-      <c r="L26" s="2" t="e">
+      <c r="L26" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41280.832709452065</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
@@ -1599,9 +1613,9 @@
       <c r="K27" t="s">
         <v>23</v>
       </c>
-      <c r="L27" s="2" t="e">
+      <c r="L27" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42238.331106899546</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
@@ -1638,9 +1652,9 @@
       <c r="K28" t="s">
         <v>17</v>
       </c>
-      <c r="L28" s="2" t="e">
+      <c r="L28" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41959.298122945991</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
@@ -1677,9 +1691,9 @@
       <c r="K29" t="s">
         <v>35</v>
       </c>
-      <c r="L29" s="2" t="e">
+      <c r="L29" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42083.364651173331</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
@@ -1716,9 +1730,9 @@
       <c r="K30" t="s">
         <v>14</v>
       </c>
-      <c r="L30" s="2" t="e">
+      <c r="L30" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41621.157016591314</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
@@ -1755,9 +1769,9 @@
       <c r="K31" t="s">
         <v>35</v>
       </c>
-      <c r="L31" s="2" t="e">
+      <c r="L31" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41984.98932000326</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
@@ -1794,9 +1808,9 @@
       <c r="K32" t="s">
         <v>20</v>
       </c>
-      <c r="L32" s="2" t="e">
+      <c r="L32" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41597.071231742251</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
@@ -1833,9 +1847,9 @@
       <c r="K33" t="s">
         <v>35</v>
       </c>
-      <c r="L33" s="2" t="e">
+      <c r="L33" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42026.798573556895</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
@@ -1872,9 +1886,9 @@
       <c r="K34" t="s">
         <v>43</v>
       </c>
-      <c r="L34" s="2" t="e">
+      <c r="L34" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41550.093135479787</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
@@ -1911,9 +1925,9 @@
       <c r="K35" t="s">
         <v>23</v>
       </c>
-      <c r="L35" s="2" t="e">
+      <c r="L35" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40719.418235759047</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
@@ -1950,9 +1964,9 @@
       <c r="K36" t="s">
         <v>37</v>
       </c>
-      <c r="L36" s="2" t="e">
+      <c r="L36" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42257.821284250684</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
@@ -1989,9 +2003,9 @@
       <c r="K37" t="s">
         <v>17</v>
       </c>
-      <c r="L37" s="2" t="e">
+      <c r="L37" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40601.743459887373</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
@@ -2028,9 +2042,9 @@
       <c r="K38" t="s">
         <v>35</v>
       </c>
-      <c r="L38" s="2" t="e">
+      <c r="L38" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41316.729106825922</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
@@ -2067,9 +2081,9 @@
       <c r="K39" t="s">
         <v>23</v>
       </c>
-      <c r="L39" s="2" t="e">
+      <c r="L39" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41921.760075289618</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
@@ -2106,9 +2120,9 @@
       <c r="K40" t="s">
         <v>14</v>
       </c>
-      <c r="L40" s="2" t="e">
+      <c r="L40" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41424.580850917228</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
@@ -2145,9 +2159,9 @@
       <c r="K41" t="s">
         <v>43</v>
       </c>
-      <c r="L41" s="2" t="e">
+      <c r="L41" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41962.157160367482</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
@@ -2184,9 +2198,9 @@
       <c r="K42" t="s">
         <v>17</v>
       </c>
-      <c r="L42" s="2" t="e">
+      <c r="L42" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41394.710109117877</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
@@ -2223,9 +2237,9 @@
       <c r="K43" t="s">
         <v>29</v>
       </c>
-      <c r="L43" s="2" t="e">
+      <c r="L43" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40633.628998277949</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
@@ -2262,9 +2276,9 @@
       <c r="K44" t="s">
         <v>20</v>
       </c>
-      <c r="L44" s="2" t="e">
+      <c r="L44" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41167.851805317114</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
@@ -2301,9 +2315,9 @@
       <c r="K45" t="s">
         <v>43</v>
       </c>
-      <c r="L45" s="2" t="e">
+      <c r="L45" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40411.986110286671</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
@@ -2340,9 +2354,9 @@
       <c r="K46" t="s">
         <v>23</v>
       </c>
-      <c r="L46" s="2" t="e">
+      <c r="L46" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40802.159007059978</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
@@ -2379,9 +2393,9 @@
       <c r="K47" t="s">
         <v>17</v>
       </c>
-      <c r="L47" s="2" t="e">
+      <c r="L47" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41532.984968452969</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
@@ -2418,9 +2432,9 @@
       <c r="K48" t="s">
         <v>43</v>
       </c>
-      <c r="L48" s="2" t="e">
+      <c r="L48" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40987.0303712366</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
@@ -2457,9 +2471,9 @@
       <c r="K49" t="s">
         <v>35</v>
       </c>
-      <c r="L49" s="2" t="e">
+      <c r="L49" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40811.823675707463</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
@@ -2496,9 +2510,9 @@
       <c r="K50" t="s">
         <v>20</v>
       </c>
-      <c r="L50" s="2" t="e">
+      <c r="L50" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41289.274553537391</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
@@ -2535,9 +2549,9 @@
       <c r="K51" t="s">
         <v>20</v>
       </c>
-      <c r="L51" s="2" t="e">
+      <c r="L51" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40641.855889563762</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
@@ -2574,9 +2588,9 @@
       <c r="K52" t="s">
         <v>20</v>
       </c>
-      <c r="L52" s="2" t="e">
+      <c r="L52" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40638.679007994149</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
@@ -2613,9 +2627,9 @@
       <c r="K53" t="s">
         <v>35</v>
       </c>
-      <c r="L53" s="2" t="e">
+      <c r="L53" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41486.325765030604</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
@@ -2652,9 +2666,9 @@
       <c r="K54" t="s">
         <v>20</v>
       </c>
-      <c r="L54" s="2" t="e">
+      <c r="L54" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40531.114664596738</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
@@ -2691,9 +2705,9 @@
       <c r="K55" t="s">
         <v>37</v>
       </c>
-      <c r="L55" s="2" t="e">
+      <c r="L55" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41574.293539278864</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
@@ -2730,9 +2744,9 @@
       <c r="K56" t="s">
         <v>17</v>
       </c>
-      <c r="L56" s="2" t="e">
+      <c r="L56" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41638.007913293848</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
@@ -2769,9 +2783,9 @@
       <c r="K57" t="s">
         <v>29</v>
       </c>
-      <c r="L57" s="2" t="e">
+      <c r="L57" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40202.536909639799</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
@@ -2808,9 +2822,9 @@
       <c r="K58" t="s">
         <v>29</v>
       </c>
-      <c r="L58" s="2" t="e">
+      <c r="L58" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41532.245098539235</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
@@ -2847,9 +2861,9 @@
       <c r="K59" t="s">
         <v>29</v>
       </c>
-      <c r="L59" s="2" t="e">
+      <c r="L59" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41100.019608116199</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
@@ -2886,9 +2900,9 @@
       <c r="K60" t="s">
         <v>35</v>
       </c>
-      <c r="L60" s="2" t="e">
+      <c r="L60" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41786.075523437939</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
@@ -2925,9 +2939,9 @@
       <c r="K61" t="s">
         <v>29</v>
       </c>
-      <c r="L61" s="2" t="e">
+      <c r="L61" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41720.96202284412</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
@@ -2964,9 +2978,9 @@
       <c r="K62" t="s">
         <v>54</v>
       </c>
-      <c r="L62" s="2" t="e">
+      <c r="L62" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42259.421021437272</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
@@ -3003,9 +3017,9 @@
       <c r="K63" t="s">
         <v>37</v>
       </c>
-      <c r="L63" s="2" t="e">
+      <c r="L63" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40203.981998977251</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
@@ -3042,9 +3056,9 @@
       <c r="K64" t="s">
         <v>20</v>
       </c>
-      <c r="L64" s="2" t="e">
+      <c r="L64" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41110.05430667317</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
@@ -3081,9 +3095,9 @@
       <c r="K65" t="s">
         <v>35</v>
       </c>
-      <c r="L65" s="2" t="e">
+      <c r="L65" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41183.092156401195</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
@@ -3120,9 +3134,9 @@
       <c r="K66" t="s">
         <v>29</v>
       </c>
-      <c r="L66" s="2" t="e">
+      <c r="L66" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41306.310313744878</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
@@ -3159,9 +3173,9 @@
       <c r="K67" t="s">
         <v>20</v>
       </c>
-      <c r="L67" s="2" t="e">
+      <c r="L67" s="2">
         <f t="shared" ref="L67:L130" ca="1" si="1">(RAND()*("14/01/2016"-"14/01/2010"+1))+"14/01/2010"</f>
-        <v>#VALUE!</v>
+        <v>41673.987135324089</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
@@ -3198,9 +3212,9 @@
       <c r="K68" t="s">
         <v>35</v>
       </c>
-      <c r="L68" s="2" t="e">
+      <c r="L68" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41083.064018675133</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
@@ -3237,9 +3251,9 @@
       <c r="K69" t="s">
         <v>17</v>
       </c>
-      <c r="L69" s="2" t="e">
+      <c r="L69" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41379.426404447047</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
@@ -3276,9 +3290,9 @@
       <c r="K70" t="s">
         <v>32</v>
       </c>
-      <c r="L70" s="2" t="e">
+      <c r="L70" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41222.730677449748</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
@@ -3315,9 +3329,9 @@
       <c r="K71" t="s">
         <v>32</v>
       </c>
-      <c r="L71" s="2" t="e">
+      <c r="L71" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42379.830829195846</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
@@ -3354,9 +3368,9 @@
       <c r="K72" t="s">
         <v>29</v>
       </c>
-      <c r="L72" s="2" t="e">
+      <c r="L72" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40303.20072873497</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
@@ -3393,9 +3407,9 @@
       <c r="K73" t="s">
         <v>35</v>
       </c>
-      <c r="L73" s="2" t="e">
+      <c r="L73" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40499.80100987621</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
@@ -3432,9 +3446,9 @@
       <c r="K74" t="s">
         <v>37</v>
       </c>
-      <c r="L74" s="2" t="e">
+      <c r="L74" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41125.696282464334</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
@@ -3471,9 +3485,9 @@
       <c r="K75" t="s">
         <v>14</v>
       </c>
-      <c r="L75" s="2" t="e">
+      <c r="L75" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40330.59107827484</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
@@ -3510,9 +3524,9 @@
       <c r="K76" t="s">
         <v>20</v>
       </c>
-      <c r="L76" s="2" t="e">
+      <c r="L76" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42054.22131064353</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
@@ -3549,9 +3563,9 @@
       <c r="K77" t="s">
         <v>29</v>
       </c>
-      <c r="L77" s="2" t="e">
+      <c r="L77" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41063.378020799406</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.3">
@@ -3588,9 +3602,9 @@
       <c r="K78" t="s">
         <v>23</v>
       </c>
-      <c r="L78" s="2" t="e">
+      <c r="L78" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41855.015277573926</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.3">
@@ -3627,9 +3641,9 @@
       <c r="K79" t="s">
         <v>54</v>
       </c>
-      <c r="L79" s="2" t="e">
+      <c r="L79" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40739.651098158502</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
@@ -3666,9 +3680,9 @@
       <c r="K80" t="s">
         <v>54</v>
       </c>
-      <c r="L80" s="2" t="e">
+      <c r="L80" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41545.308243055275</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
@@ -3705,9 +3719,9 @@
       <c r="K81" t="s">
         <v>17</v>
       </c>
-      <c r="L81" s="2" t="e">
+      <c r="L81" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41523.662061873576</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.3">
@@ -3744,9 +3758,9 @@
       <c r="K82" t="s">
         <v>54</v>
       </c>
-      <c r="L82" s="2" t="e">
+      <c r="L82" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40755.358465576021</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.3">
@@ -3783,9 +3797,9 @@
       <c r="K83" t="s">
         <v>32</v>
       </c>
-      <c r="L83" s="2" t="e">
+      <c r="L83" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42311.839747726066</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.3">
@@ -3822,9 +3836,9 @@
       <c r="K84" t="s">
         <v>37</v>
       </c>
-      <c r="L84" s="2" t="e">
+      <c r="L84" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40792.707760319747</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.3">
@@ -3861,9 +3875,9 @@
       <c r="K85" t="s">
         <v>29</v>
       </c>
-      <c r="L85" s="2" t="e">
+      <c r="L85" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41152.172433156687</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.3">
@@ -3900,9 +3914,9 @@
       <c r="K86" t="s">
         <v>32</v>
       </c>
-      <c r="L86" s="2" t="e">
+      <c r="L86" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41537.808969134639</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.3">
@@ -3939,9 +3953,9 @@
       <c r="K87" t="s">
         <v>20</v>
       </c>
-      <c r="L87" s="2" t="e">
+      <c r="L87" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41258.52942495561</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.3">
@@ -3978,9 +3992,9 @@
       <c r="K88" t="s">
         <v>43</v>
       </c>
-      <c r="L88" s="2" t="e">
+      <c r="L88" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41681.698393161809</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.3">
@@ -4017,9 +4031,9 @@
       <c r="K89" t="s">
         <v>32</v>
       </c>
-      <c r="L89" s="2" t="e">
+      <c r="L89" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42359.911026680464</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.3">
@@ -4056,9 +4070,9 @@
       <c r="K90" t="s">
         <v>37</v>
       </c>
-      <c r="L90" s="2" t="e">
+      <c r="L90" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42073.81701499677</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.3">
@@ -4095,9 +4109,9 @@
       <c r="K91" t="s">
         <v>43</v>
       </c>
-      <c r="L91" s="2" t="e">
+      <c r="L91" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40229.373303788467</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.3">
@@ -4134,9 +4148,9 @@
       <c r="K92" t="s">
         <v>43</v>
       </c>
-      <c r="L92" s="2" t="e">
+      <c r="L92" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40957.926121446348</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.3">
@@ -4173,9 +4187,9 @@
       <c r="K93" t="s">
         <v>23</v>
       </c>
-      <c r="L93" s="2" t="e">
+      <c r="L93" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42306.562043239261</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.3">
@@ -4212,9 +4226,9 @@
       <c r="K94" t="s">
         <v>54</v>
       </c>
-      <c r="L94" s="2" t="e">
+      <c r="L94" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40311.600029359601</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.3">
@@ -4251,9 +4265,9 @@
       <c r="K95" t="s">
         <v>37</v>
       </c>
-      <c r="L95" s="2" t="e">
+      <c r="L95" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40755.803498953152</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.3">
@@ -4290,9 +4304,9 @@
       <c r="K96" t="s">
         <v>17</v>
       </c>
-      <c r="L96" s="2" t="e">
+      <c r="L96" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40262.562776952254</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.3">
@@ -4329,9 +4343,9 @@
       <c r="K97" t="s">
         <v>14</v>
       </c>
-      <c r="L97" s="2" t="e">
+      <c r="L97" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41907.944517455173</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
@@ -4368,9 +4382,9 @@
       <c r="K98" t="s">
         <v>17</v>
       </c>
-      <c r="L98" s="2" t="e">
+      <c r="L98" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40725.260231120905</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.3">
@@ -4407,9 +4421,9 @@
       <c r="K99" t="s">
         <v>23</v>
       </c>
-      <c r="L99" s="2" t="e">
+      <c r="L99" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40731.830369873212</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.3">
@@ -4446,9 +4460,9 @@
       <c r="K100" t="s">
         <v>29</v>
       </c>
-      <c r="L100" s="2" t="e">
+      <c r="L100" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41706.952967050041</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.3">
@@ -4485,9 +4499,9 @@
       <c r="K101" t="s">
         <v>23</v>
       </c>
-      <c r="L101" s="2" t="e">
+      <c r="L101" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41135.101511026216</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.3">
@@ -4524,9 +4538,9 @@
       <c r="K102" t="s">
         <v>35</v>
       </c>
-      <c r="L102" s="2" t="e">
+      <c r="L102" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41879.156075657927</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.3">
@@ -4563,9 +4577,9 @@
       <c r="K103" t="s">
         <v>32</v>
       </c>
-      <c r="L103" s="2" t="e">
+      <c r="L103" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40490.289666581877</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.3">
@@ -4602,9 +4616,9 @@
       <c r="K104" t="s">
         <v>43</v>
       </c>
-      <c r="L104" s="2" t="e">
+      <c r="L104" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41117.692533466034</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.3">
@@ -4641,9 +4655,9 @@
       <c r="K105" t="s">
         <v>23</v>
       </c>
-      <c r="L105" s="2" t="e">
+      <c r="L105" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41103.97213780538</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.3">
@@ -4680,9 +4694,9 @@
       <c r="K106" t="s">
         <v>29</v>
       </c>
-      <c r="L106" s="2" t="e">
+      <c r="L106" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42071.693016486759</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.3">
@@ -4719,9 +4733,9 @@
       <c r="K107" t="s">
         <v>29</v>
       </c>
-      <c r="L107" s="2" t="e">
+      <c r="L107" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41204.609393386148</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.3">
@@ -4758,9 +4772,9 @@
       <c r="K108" t="s">
         <v>43</v>
       </c>
-      <c r="L108" s="2" t="e">
+      <c r="L108" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41817.793187606774</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.3">
@@ -4797,9 +4811,9 @@
       <c r="K109" t="s">
         <v>17</v>
       </c>
-      <c r="L109" s="2" t="e">
+      <c r="L109" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42225.967064214892</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
@@ -4836,9 +4850,9 @@
       <c r="K110" t="s">
         <v>54</v>
       </c>
-      <c r="L110" s="2" t="e">
+      <c r="L110" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40315.693806656098</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.3">
@@ -4875,9 +4889,9 @@
       <c r="K111" t="s">
         <v>14</v>
       </c>
-      <c r="L111" s="2" t="e">
+      <c r="L111" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42010.182520076189</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.3">
@@ -4914,9 +4928,9 @@
       <c r="K112" t="s">
         <v>20</v>
       </c>
-      <c r="L112" s="2" t="e">
+      <c r="L112" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40250.895222599749</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.3">
@@ -4953,9 +4967,9 @@
       <c r="K113" t="s">
         <v>32</v>
       </c>
-      <c r="L113" s="2" t="e">
+      <c r="L113" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41977.968734257745</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.3">
@@ -4992,9 +5006,9 @@
       <c r="K114" t="s">
         <v>37</v>
       </c>
-      <c r="L114" s="2" t="e">
+      <c r="L114" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41005.060473550991</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.3">
@@ -5031,9 +5045,9 @@
       <c r="K115" t="s">
         <v>54</v>
       </c>
-      <c r="L115" s="2" t="e">
+      <c r="L115" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42368.756692694325</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.3">
@@ -5070,9 +5084,9 @@
       <c r="K116" t="s">
         <v>32</v>
       </c>
-      <c r="L116" s="2" t="e">
+      <c r="L116" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40526.113507349415</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.3">
@@ -5109,9 +5123,9 @@
       <c r="K117" t="s">
         <v>35</v>
       </c>
-      <c r="L117" s="2" t="e">
+      <c r="L117" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42335.81428146136</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.3">
@@ -5148,9 +5162,9 @@
       <c r="K118" t="s">
         <v>32</v>
       </c>
-      <c r="L118" s="2" t="e">
+      <c r="L118" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41511.545293404386</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.3">
@@ -5187,9 +5201,9 @@
       <c r="K119" t="s">
         <v>54</v>
       </c>
-      <c r="L119" s="2" t="e">
+      <c r="L119" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42174.165959868988</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.3">
@@ -5226,9 +5240,9 @@
       <c r="K120" t="s">
         <v>54</v>
       </c>
-      <c r="L120" s="2" t="e">
+      <c r="L120" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41662.977343561761</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.3">
@@ -5265,9 +5279,9 @@
       <c r="K121" t="s">
         <v>29</v>
       </c>
-      <c r="L121" s="2" t="e">
+      <c r="L121" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41054.195529966877</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.3">
@@ -5304,9 +5318,9 @@
       <c r="K122" t="s">
         <v>29</v>
       </c>
-      <c r="L122" s="2" t="e">
+      <c r="L122" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41233.901228344534</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.3">
@@ -5343,9 +5357,9 @@
       <c r="K123" t="s">
         <v>29</v>
       </c>
-      <c r="L123" s="2" t="e">
+      <c r="L123" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40906.336338781453</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.3">
@@ -5382,9 +5396,9 @@
       <c r="K124" t="s">
         <v>35</v>
       </c>
-      <c r="L124" s="2" t="e">
+      <c r="L124" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41214.350292554082</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.3">
@@ -5421,9 +5435,9 @@
       <c r="K125" t="s">
         <v>20</v>
       </c>
-      <c r="L125" s="2" t="e">
+      <c r="L125" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40989.314711202314</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.3">
@@ -5460,9 +5474,9 @@
       <c r="K126" t="s">
         <v>37</v>
       </c>
-      <c r="L126" s="2" t="e">
+      <c r="L126" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42060.402428016831</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.3">
@@ -5499,9 +5513,9 @@
       <c r="K127" t="s">
         <v>37</v>
       </c>
-      <c r="L127" s="2" t="e">
+      <c r="L127" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41356.253361910349</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.3">
@@ -5538,9 +5552,9 @@
       <c r="K128" t="s">
         <v>54</v>
       </c>
-      <c r="L128" s="2" t="e">
+      <c r="L128" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40653.955752784539</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.3">
@@ -5577,9 +5591,9 @@
       <c r="K129" t="s">
         <v>20</v>
       </c>
-      <c r="L129" s="2" t="e">
+      <c r="L129" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41430.942331605576</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.3">
@@ -5616,9 +5630,9 @@
       <c r="K130" t="s">
         <v>29</v>
       </c>
-      <c r="L130" s="2" t="e">
+      <c r="L130" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41916.83832268753</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.3">
@@ -5655,9 +5669,9 @@
       <c r="K131" t="s">
         <v>23</v>
       </c>
-      <c r="L131" s="2" t="e">
+      <c r="L131" s="2">
         <f t="shared" ref="L131:L194" ca="1" si="2">(RAND()*("14/01/2016"-"14/01/2010"+1))+"14/01/2010"</f>
-        <v>#VALUE!</v>
+        <v>41792.972513977831</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.3">
@@ -5694,9 +5708,9 @@
       <c r="K132" t="s">
         <v>37</v>
       </c>
-      <c r="L132" s="2" t="e">
+      <c r="L132" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41546.835323932726</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.3">
@@ -5733,9 +5747,9 @@
       <c r="K133" t="s">
         <v>35</v>
       </c>
-      <c r="L133" s="2" t="e">
+      <c r="L133" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41734.079255822493</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.3">
@@ -5772,9 +5786,9 @@
       <c r="K134" t="s">
         <v>17</v>
       </c>
-      <c r="L134" s="2" t="e">
+      <c r="L134" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41720.629786892023</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.3">
@@ -5811,9 +5825,9 @@
       <c r="K135" t="s">
         <v>43</v>
       </c>
-      <c r="L135" s="2" t="e">
+      <c r="L135" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41205.294785353261</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.3">
@@ -5850,9 +5864,9 @@
       <c r="K136" t="s">
         <v>37</v>
       </c>
-      <c r="L136" s="2" t="e">
+      <c r="L136" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41899.321534688104</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.3">
@@ -5889,9 +5903,9 @@
       <c r="K137" t="s">
         <v>23</v>
       </c>
-      <c r="L137" s="2" t="e">
+      <c r="L137" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>42122.226563379962</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.3">
@@ -5928,9 +5942,9 @@
       <c r="K138" t="s">
         <v>37</v>
       </c>
-      <c r="L138" s="2" t="e">
+      <c r="L138" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41641.339509562626</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.3">
@@ -5967,9 +5981,9 @@
       <c r="K139" t="s">
         <v>23</v>
       </c>
-      <c r="L139" s="2" t="e">
+      <c r="L139" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40893.207101365413</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.3">
@@ -6006,9 +6020,9 @@
       <c r="K140" t="s">
         <v>20</v>
       </c>
-      <c r="L140" s="2" t="e">
+      <c r="L140" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40401.846421310693</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.3">
@@ -6045,9 +6059,9 @@
       <c r="K141" t="s">
         <v>35</v>
       </c>
-      <c r="L141" s="2" t="e">
+      <c r="L141" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40781.137946879637</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.3">
@@ -6084,9 +6098,9 @@
       <c r="K142" t="s">
         <v>37</v>
       </c>
-      <c r="L142" s="2" t="e">
+      <c r="L142" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40239.852477828841</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.3">
@@ -6123,9 +6137,9 @@
       <c r="K143" t="s">
         <v>35</v>
       </c>
-      <c r="L143" s="2" t="e">
+      <c r="L143" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41435.8093911736</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.3">
@@ -6162,9 +6176,9 @@
       <c r="K144" t="s">
         <v>32</v>
       </c>
-      <c r="L144" s="2" t="e">
+      <c r="L144" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40560.37586887864</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.3">
@@ -6201,9 +6215,9 @@
       <c r="K145" t="s">
         <v>23</v>
       </c>
-      <c r="L145" s="2" t="e">
+      <c r="L145" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>42337.7451595815</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.3">
@@ -6240,9 +6254,9 @@
       <c r="K146" t="s">
         <v>54</v>
       </c>
-      <c r="L146" s="2" t="e">
+      <c r="L146" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41776.986416237458</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.3">
@@ -6279,9 +6293,9 @@
       <c r="K147" t="s">
         <v>20</v>
       </c>
-      <c r="L147" s="2" t="e">
+      <c r="L147" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41740.048981633452</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.3">
@@ -6318,9 +6332,9 @@
       <c r="K148" t="s">
         <v>43</v>
       </c>
-      <c r="L148" s="2" t="e">
+      <c r="L148" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41218.080425903638</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.3">
@@ -6357,9 +6371,9 @@
       <c r="K149" t="s">
         <v>43</v>
       </c>
-      <c r="L149" s="2" t="e">
+      <c r="L149" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41759.381652964526</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.3">
@@ -6396,9 +6410,9 @@
       <c r="K150" t="s">
         <v>23</v>
       </c>
-      <c r="L150" s="2" t="e">
+      <c r="L150" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>42165.859539315483</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.3">
@@ -6435,9 +6449,9 @@
       <c r="K151" t="s">
         <v>37</v>
       </c>
-      <c r="L151" s="2" t="e">
+      <c r="L151" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40479.752964038824</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.3">
@@ -6474,9 +6488,9 @@
       <c r="K152" t="s">
         <v>37</v>
       </c>
-      <c r="L152" s="2" t="e">
+      <c r="L152" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40232.540014099628</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.3">
@@ -6513,9 +6527,9 @@
       <c r="K153" t="s">
         <v>23</v>
       </c>
-      <c r="L153" s="2" t="e">
+      <c r="L153" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>42171.284815518986</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.3">
@@ -6552,9 +6566,9 @@
       <c r="K154" t="s">
         <v>29</v>
       </c>
-      <c r="L154" s="2" t="e">
+      <c r="L154" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40264.352838435887</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.3">
@@ -6591,9 +6605,9 @@
       <c r="K155" t="s">
         <v>17</v>
       </c>
-      <c r="L155" s="2" t="e">
+      <c r="L155" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41790.278571953721</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.3">
@@ -6630,9 +6644,9 @@
       <c r="K156" t="s">
         <v>17</v>
       </c>
-      <c r="L156" s="2" t="e">
+      <c r="L156" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40730.669827114383</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.3">
@@ -6669,9 +6683,9 @@
       <c r="K157" t="s">
         <v>37</v>
       </c>
-      <c r="L157" s="2" t="e">
+      <c r="L157" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41879.200151144876</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.3">
@@ -6708,9 +6722,9 @@
       <c r="K158" t="s">
         <v>54</v>
       </c>
-      <c r="L158" s="2" t="e">
+      <c r="L158" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40718.448868456573</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.3">
@@ -6747,9 +6761,9 @@
       <c r="K159" t="s">
         <v>32</v>
       </c>
-      <c r="L159" s="2" t="e">
+      <c r="L159" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41275.208795736959</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.3">
@@ -6786,9 +6800,9 @@
       <c r="K160" t="s">
         <v>23</v>
       </c>
-      <c r="L160" s="2" t="e">
+      <c r="L160" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41773.721569138041</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.3">
@@ -6825,9 +6839,9 @@
       <c r="K161" t="s">
         <v>20</v>
       </c>
-      <c r="L161" s="2" t="e">
+      <c r="L161" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>42152.591762596225</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.3">
@@ -6864,9 +6878,9 @@
       <c r="K162" t="s">
         <v>14</v>
       </c>
-      <c r="L162" s="2" t="e">
+      <c r="L162" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41717.156983035296</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.3">
@@ -6903,9 +6917,9 @@
       <c r="K163" t="s">
         <v>37</v>
       </c>
-      <c r="L163" s="2" t="e">
+      <c r="L163" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>42314.346583269158</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.3">
@@ -6942,9 +6956,9 @@
       <c r="K164" t="s">
         <v>37</v>
       </c>
-      <c r="L164" s="2" t="e">
+      <c r="L164" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40868.747711491022</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.3">
@@ -6981,9 +6995,9 @@
       <c r="K165" t="s">
         <v>37</v>
       </c>
-      <c r="L165" s="2" t="e">
+      <c r="L165" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41591.955268023041</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.3">
@@ -7020,9 +7034,9 @@
       <c r="K166" t="s">
         <v>54</v>
       </c>
-      <c r="L166" s="2" t="e">
+      <c r="L166" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41179.465384432755</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.3">
@@ -7059,9 +7073,9 @@
       <c r="K167" t="s">
         <v>17</v>
       </c>
-      <c r="L167" s="2" t="e">
+      <c r="L167" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41683.501311574597</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.3">
@@ -7098,9 +7112,9 @@
       <c r="K168" t="s">
         <v>54</v>
       </c>
-      <c r="L168" s="2" t="e">
+      <c r="L168" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40644.64663512366</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.3">
@@ -7137,9 +7151,9 @@
       <c r="K169" t="s">
         <v>17</v>
       </c>
-      <c r="L169" s="2" t="e">
+      <c r="L169" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41794.547397384682</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.3">
@@ -7176,9 +7190,9 @@
       <c r="K170" t="s">
         <v>23</v>
       </c>
-      <c r="L170" s="2" t="e">
+      <c r="L170" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40859.598825565598</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.3">
@@ -7215,9 +7229,9 @@
       <c r="K171" t="s">
         <v>35</v>
       </c>
-      <c r="L171" s="2" t="e">
+      <c r="L171" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>42061.069704469723</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.3">
@@ -7254,9 +7268,9 @@
       <c r="K172" t="s">
         <v>23</v>
       </c>
-      <c r="L172" s="2" t="e">
+      <c r="L172" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40493.936385862966</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.3">
@@ -7293,9 +7307,9 @@
       <c r="K173" t="s">
         <v>14</v>
       </c>
-      <c r="L173" s="2" t="e">
+      <c r="L173" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>42016.994818407577</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.3">
@@ -7332,9 +7346,9 @@
       <c r="K174" t="s">
         <v>20</v>
       </c>
-      <c r="L174" s="2" t="e">
+      <c r="L174" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41741.72901582795</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.3">
@@ -7371,9 +7385,9 @@
       <c r="K175" t="s">
         <v>17</v>
       </c>
-      <c r="L175" s="2" t="e">
+      <c r="L175" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>42214.382750726945</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.3">
@@ -7410,9 +7424,9 @@
       <c r="K176" t="s">
         <v>54</v>
       </c>
-      <c r="L176" s="2" t="e">
+      <c r="L176" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41821.776452367121</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.3">
@@ -7449,9 +7463,9 @@
       <c r="K177" t="s">
         <v>29</v>
       </c>
-      <c r="L177" s="2" t="e">
+      <c r="L177" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41466.123440235904</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.3">
@@ -7488,9 +7502,9 @@
       <c r="K178" t="s">
         <v>37</v>
       </c>
-      <c r="L178" s="2" t="e">
+      <c r="L178" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40266.045101107644</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.3">
@@ -7527,9 +7541,9 @@
       <c r="K179" t="s">
         <v>23</v>
       </c>
-      <c r="L179" s="2" t="e">
+      <c r="L179" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>42067.609188418326</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.3">
@@ -7566,9 +7580,9 @@
       <c r="K180" t="s">
         <v>35</v>
       </c>
-      <c r="L180" s="2" t="e">
+      <c r="L180" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41919.729368701315</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.3">
@@ -7605,9 +7619,9 @@
       <c r="K181" t="s">
         <v>29</v>
       </c>
-      <c r="L181" s="2" t="e">
+      <c r="L181" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41601.485624856461</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.3">
@@ -7644,9 +7658,9 @@
       <c r="K182" t="s">
         <v>43</v>
       </c>
-      <c r="L182" s="2" t="e">
+      <c r="L182" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40638.579532942342</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.3">
@@ -7683,9 +7697,9 @@
       <c r="K183" t="s">
         <v>54</v>
       </c>
-      <c r="L183" s="2" t="e">
+      <c r="L183" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41860.518070091734</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.3">
@@ -7722,9 +7736,9 @@
       <c r="K184" t="s">
         <v>29</v>
       </c>
-      <c r="L184" s="2" t="e">
+      <c r="L184" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40975.998243936316</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.3">
@@ -7761,9 +7775,9 @@
       <c r="K185" t="s">
         <v>37</v>
       </c>
-      <c r="L185" s="2" t="e">
+      <c r="L185" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>42251.827821998857</v>
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.3">
@@ -7800,9 +7814,9 @@
       <c r="K186" t="s">
         <v>54</v>
       </c>
-      <c r="L186" s="2" t="e">
+      <c r="L186" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40739.712071450973</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.3">
@@ -7839,9 +7853,9 @@
       <c r="K187" t="s">
         <v>43</v>
       </c>
-      <c r="L187" s="2" t="e">
+      <c r="L187" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40863.483303239249</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.3">
@@ -7878,9 +7892,9 @@
       <c r="K188" t="s">
         <v>32</v>
       </c>
-      <c r="L188" s="2" t="e">
+      <c r="L188" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41609.138858686558</v>
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.3">
@@ -7917,9 +7931,9 @@
       <c r="K189" t="s">
         <v>20</v>
       </c>
-      <c r="L189" s="2" t="e">
+      <c r="L189" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41733.471910140972</v>
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.3">
@@ -7956,9 +7970,9 @@
       <c r="K190" t="s">
         <v>29</v>
       </c>
-      <c r="L190" s="2" t="e">
+      <c r="L190" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40455.250460984913</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.3">
@@ -7995,9 +8009,9 @@
       <c r="K191" t="s">
         <v>23</v>
       </c>
-      <c r="L191" s="2" t="e">
+      <c r="L191" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41223.825126557174</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.3">
@@ -8034,9 +8048,9 @@
       <c r="K192" t="s">
         <v>14</v>
       </c>
-      <c r="L192" s="2" t="e">
+      <c r="L192" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>42197.142771757033</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.3">
@@ -8073,9 +8087,9 @@
       <c r="K193" t="s">
         <v>29</v>
       </c>
-      <c r="L193" s="2" t="e">
+      <c r="L193" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41987.347346935392</v>
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.3">
@@ -8112,9 +8126,9 @@
       <c r="K194" t="s">
         <v>43</v>
       </c>
-      <c r="L194" s="2" t="e">
+      <c r="L194" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40995.292450199551</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.3">
@@ -8151,9 +8165,9 @@
       <c r="K195" t="s">
         <v>54</v>
       </c>
-      <c r="L195" s="2" t="e">
+      <c r="L195" s="2">
         <f t="shared" ref="L195:L258" ca="1" si="3">(RAND()*("14/01/2016"-"14/01/2010"+1))+"14/01/2010"</f>
-        <v>#VALUE!</v>
+        <v>42076.379450871776</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.3">
@@ -8190,9 +8204,9 @@
       <c r="K196" t="s">
         <v>35</v>
       </c>
-      <c r="L196" s="2" t="e">
+      <c r="L196" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40748.605594974433</v>
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.3">
@@ -8229,9 +8243,9 @@
       <c r="K197" t="s">
         <v>37</v>
       </c>
-      <c r="L197" s="2" t="e">
+      <c r="L197" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40301.170728874393</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.3">
@@ -8268,9 +8282,9 @@
       <c r="K198" t="s">
         <v>23</v>
       </c>
-      <c r="L198" s="2" t="e">
+      <c r="L198" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>42184.219442933078</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.3">
@@ -8307,9 +8321,9 @@
       <c r="K199" t="s">
         <v>29</v>
       </c>
-      <c r="L199" s="2" t="e">
+      <c r="L199" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41990.957785339022</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.3">
@@ -8346,9 +8360,9 @@
       <c r="K200" t="s">
         <v>17</v>
       </c>
-      <c r="L200" s="2" t="e">
+      <c r="L200" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41128.505317584953</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.3">
@@ -8385,9 +8399,9 @@
       <c r="K201" t="s">
         <v>20</v>
       </c>
-      <c r="L201" s="2" t="e">
+      <c r="L201" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40509.278937805931</v>
       </c>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.3">
@@ -8424,9 +8438,9 @@
       <c r="K202" t="s">
         <v>54</v>
       </c>
-      <c r="L202" s="2" t="e">
+      <c r="L202" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>42012.702969327001</v>
       </c>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.3">
@@ -8463,9 +8477,9 @@
       <c r="K203" t="s">
         <v>14</v>
       </c>
-      <c r="L203" s="2" t="e">
+      <c r="L203" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41205.004318115585</v>
       </c>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.3">
@@ -8502,9 +8516,9 @@
       <c r="K204" t="s">
         <v>20</v>
       </c>
-      <c r="L204" s="2" t="e">
+      <c r="L204" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41116.994103188772</v>
       </c>
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.3">
@@ -8541,9 +8555,9 @@
       <c r="K205" t="s">
         <v>20</v>
       </c>
-      <c r="L205" s="2" t="e">
+      <c r="L205" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41145.857301085802</v>
       </c>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.3">
@@ -8580,9 +8594,9 @@
       <c r="K206" t="s">
         <v>37</v>
       </c>
-      <c r="L206" s="2" t="e">
+      <c r="L206" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40510.618615219144</v>
       </c>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.3">
@@ -8619,9 +8633,9 @@
       <c r="K207" t="s">
         <v>43</v>
       </c>
-      <c r="L207" s="2" t="e">
+      <c r="L207" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41978.096626106242</v>
       </c>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.3">
@@ -8658,9 +8672,9 @@
       <c r="K208" t="s">
         <v>14</v>
       </c>
-      <c r="L208" s="2" t="e">
+      <c r="L208" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40566.227650539222</v>
       </c>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.3">
@@ -8697,9 +8711,9 @@
       <c r="K209" t="s">
         <v>54</v>
       </c>
-      <c r="L209" s="2" t="e">
+      <c r="L209" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41740.295888312925</v>
       </c>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.3">
@@ -8736,9 +8750,9 @@
       <c r="K210" t="s">
         <v>29</v>
       </c>
-      <c r="L210" s="2" t="e">
+      <c r="L210" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41878.734495737037</v>
       </c>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.3">
@@ -8775,9 +8789,9 @@
       <c r="K211" t="s">
         <v>14</v>
       </c>
-      <c r="L211" s="2" t="e">
+      <c r="L211" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41758.160589274987</v>
       </c>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.3">
@@ -8814,9 +8828,9 @@
       <c r="K212" t="s">
         <v>37</v>
       </c>
-      <c r="L212" s="2" t="e">
+      <c r="L212" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41821.059371831194</v>
       </c>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.3">
@@ -8853,9 +8867,9 @@
       <c r="K213" t="s">
         <v>14</v>
       </c>
-      <c r="L213" s="2" t="e">
+      <c r="L213" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41441.465794065211</v>
       </c>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.3">
@@ -8892,9 +8906,9 @@
       <c r="K214" t="s">
         <v>23</v>
       </c>
-      <c r="L214" s="2" t="e">
+      <c r="L214" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40275.600127137142</v>
       </c>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.3">
@@ -8931,9 +8945,9 @@
       <c r="K215" t="s">
         <v>54</v>
       </c>
-      <c r="L215" s="2" t="e">
+      <c r="L215" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>42255.225098420073</v>
       </c>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.3">
@@ -8970,9 +8984,9 @@
       <c r="K216" t="s">
         <v>14</v>
       </c>
-      <c r="L216" s="2" t="e">
+      <c r="L216" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41482.029314718427</v>
       </c>
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.3">
@@ -9009,9 +9023,9 @@
       <c r="K217" t="s">
         <v>29</v>
       </c>
-      <c r="L217" s="2" t="e">
+      <c r="L217" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>42013.498800896981</v>
       </c>
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.3">
@@ -9048,9 +9062,9 @@
       <c r="K218" t="s">
         <v>29</v>
       </c>
-      <c r="L218" s="2" t="e">
+      <c r="L218" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41881.606166081991</v>
       </c>
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.3">
@@ -9087,9 +9101,9 @@
       <c r="K219" t="s">
         <v>43</v>
       </c>
-      <c r="L219" s="2" t="e">
+      <c r="L219" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41371.64301451559</v>
       </c>
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.3">
@@ -9126,9 +9140,9 @@
       <c r="K220" t="s">
         <v>37</v>
       </c>
-      <c r="L220" s="2" t="e">
+      <c r="L220" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41994.268493129857</v>
       </c>
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.3">
@@ -9165,9 +9179,9 @@
       <c r="K221" t="s">
         <v>43</v>
       </c>
-      <c r="L221" s="2" t="e">
+      <c r="L221" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40771.369392861037</v>
       </c>
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.3">
@@ -9204,9 +9218,9 @@
       <c r="K222" t="s">
         <v>20</v>
       </c>
-      <c r="L222" s="2" t="e">
+      <c r="L222" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>42178.796774841911</v>
       </c>
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.3">
@@ -9243,9 +9257,9 @@
       <c r="K223" t="s">
         <v>23</v>
       </c>
-      <c r="L223" s="2" t="e">
+      <c r="L223" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41352.566774537816</v>
       </c>
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.3">
@@ -9282,9 +9296,9 @@
       <c r="K224" t="s">
         <v>43</v>
       </c>
-      <c r="L224" s="2" t="e">
+      <c r="L224" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40534.53249075418</v>
       </c>
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.3">
@@ -9321,9 +9335,9 @@
       <c r="K225" t="s">
         <v>37</v>
       </c>
-      <c r="L225" s="2" t="e">
+      <c r="L225" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>42152.532705091333</v>
       </c>
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.3">
@@ -9360,9 +9374,9 @@
       <c r="K226" t="s">
         <v>35</v>
       </c>
-      <c r="L226" s="2" t="e">
+      <c r="L226" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41076.62415769037</v>
       </c>
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.3">
@@ -9399,9 +9413,9 @@
       <c r="K227" t="s">
         <v>14</v>
       </c>
-      <c r="L227" s="2" t="e">
+      <c r="L227" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40289.234659097623</v>
       </c>
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.3">
@@ -9438,9 +9452,9 @@
       <c r="K228" t="s">
         <v>23</v>
       </c>
-      <c r="L228" s="2" t="e">
+      <c r="L228" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41389.019139283126</v>
       </c>
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.3">
@@ -9477,9 +9491,9 @@
       <c r="K229" t="s">
         <v>54</v>
       </c>
-      <c r="L229" s="2" t="e">
+      <c r="L229" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41416.426283736371</v>
       </c>
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.3">
@@ -9516,9 +9530,9 @@
       <c r="K230" t="s">
         <v>23</v>
       </c>
-      <c r="L230" s="2" t="e">
+      <c r="L230" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40193.116679336199</v>
       </c>
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.3">
@@ -9555,9 +9569,9 @@
       <c r="K231" t="s">
         <v>14</v>
       </c>
-      <c r="L231" s="2" t="e">
+      <c r="L231" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41284.651139361362</v>
       </c>
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.3">
@@ -9594,9 +9608,9 @@
       <c r="K232" t="s">
         <v>43</v>
       </c>
-      <c r="L232" s="2" t="e">
+      <c r="L232" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40975.200210549403</v>
       </c>
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.3">
@@ -9633,9 +9647,9 @@
       <c r="K233" t="s">
         <v>37</v>
       </c>
-      <c r="L233" s="2" t="e">
+      <c r="L233" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41507.556517508587</v>
       </c>
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.3">
@@ -9672,9 +9686,9 @@
       <c r="K234" t="s">
         <v>32</v>
       </c>
-      <c r="L234" s="2" t="e">
+      <c r="L234" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40831.155702983524</v>
       </c>
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.3">
@@ -9711,9 +9725,9 @@
       <c r="K235" t="s">
         <v>17</v>
       </c>
-      <c r="L235" s="2" t="e">
+      <c r="L235" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40707.268979262168</v>
       </c>
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.3">
@@ -9750,9 +9764,9 @@
       <c r="K236" t="s">
         <v>23</v>
       </c>
-      <c r="L236" s="2" t="e">
+      <c r="L236" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40404.463706182905</v>
       </c>
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.3">
@@ -9789,9 +9803,9 @@
       <c r="K237" t="s">
         <v>29</v>
       </c>
-      <c r="L237" s="2" t="e">
+      <c r="L237" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40586.60705595406</v>
       </c>
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.3">
@@ -9828,9 +9842,9 @@
       <c r="K238" t="s">
         <v>20</v>
       </c>
-      <c r="L238" s="2" t="e">
+      <c r="L238" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41716.794519501098</v>
       </c>
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.3">
@@ -9867,9 +9881,9 @@
       <c r="K239" t="s">
         <v>14</v>
       </c>
-      <c r="L239" s="2" t="e">
+      <c r="L239" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40698.037465919668</v>
       </c>
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.3">
@@ -9906,9 +9920,9 @@
       <c r="K240" t="s">
         <v>14</v>
       </c>
-      <c r="L240" s="2" t="e">
+      <c r="L240" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40882.877606904571</v>
       </c>
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.3">
@@ -9945,9 +9959,9 @@
       <c r="K241" t="s">
         <v>43</v>
       </c>
-      <c r="L241" s="2" t="e">
+      <c r="L241" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40223.360976470474</v>
       </c>
     </row>
     <row r="242" spans="1:12" x14ac:dyDescent="0.3">
@@ -9984,9 +9998,9 @@
       <c r="K242" t="s">
         <v>37</v>
       </c>
-      <c r="L242" s="2" t="e">
+      <c r="L242" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41324.889818634423</v>
       </c>
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.3">
@@ -10023,9 +10037,9 @@
       <c r="K243" t="s">
         <v>43</v>
       </c>
-      <c r="L243" s="2" t="e">
+      <c r="L243" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>42177.653803097841</v>
       </c>
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.3">
@@ -10062,9 +10076,9 @@
       <c r="K244" t="s">
         <v>54</v>
       </c>
-      <c r="L244" s="2" t="e">
+      <c r="L244" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41284.614772150846</v>
       </c>
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.3">
@@ -10101,9 +10115,9 @@
       <c r="K245" t="s">
         <v>37</v>
       </c>
-      <c r="L245" s="2" t="e">
+      <c r="L245" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>42214.199538304638</v>
       </c>
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.3">
@@ -10140,9 +10154,9 @@
       <c r="K246" t="s">
         <v>43</v>
       </c>
-      <c r="L246" s="2" t="e">
+      <c r="L246" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40828.23888084817</v>
       </c>
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.3">
@@ -10179,9 +10193,9 @@
       <c r="K247" t="s">
         <v>14</v>
       </c>
-      <c r="L247" s="2" t="e">
+      <c r="L247" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40363.963613741827</v>
       </c>
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.3">
@@ -10218,9 +10232,9 @@
       <c r="K248" t="s">
         <v>54</v>
       </c>
-      <c r="L248" s="2" t="e">
+      <c r="L248" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>42093.392799557936</v>
       </c>
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.3">
@@ -10257,9 +10271,9 @@
       <c r="K249" t="s">
         <v>32</v>
       </c>
-      <c r="L249" s="2" t="e">
+      <c r="L249" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40613.705752469534</v>
       </c>
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.3">
@@ -10296,9 +10310,9 @@
       <c r="K250" t="s">
         <v>35</v>
       </c>
-      <c r="L250" s="2" t="e">
+      <c r="L250" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40863.880726682371</v>
       </c>
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.3">
@@ -10335,9 +10349,9 @@
       <c r="K251" t="s">
         <v>20</v>
       </c>
-      <c r="L251" s="2" t="e">
+      <c r="L251" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>42334.559051991826</v>
       </c>
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.3">
@@ -10374,9 +10388,9 @@
       <c r="K252" t="s">
         <v>43</v>
       </c>
-      <c r="L252" s="2" t="e">
+      <c r="L252" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40815.354161497715</v>
       </c>
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.3">
@@ -10413,9 +10427,9 @@
       <c r="K253" t="s">
         <v>20</v>
       </c>
-      <c r="L253" s="2" t="e">
+      <c r="L253" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41295.835897754259</v>
       </c>
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.3">
@@ -10452,9 +10466,9 @@
       <c r="K254" t="s">
         <v>14</v>
       </c>
-      <c r="L254" s="2" t="e">
+      <c r="L254" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41139.329057519986</v>
       </c>
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.3">
@@ -10491,9 +10505,9 @@
       <c r="K255" t="s">
         <v>14</v>
       </c>
-      <c r="L255" s="2" t="e">
+      <c r="L255" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41835.38035006827</v>
       </c>
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.3">
@@ -10530,9 +10544,9 @@
       <c r="K256" t="s">
         <v>35</v>
       </c>
-      <c r="L256" s="2" t="e">
+      <c r="L256" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>42382.673143834603</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.3">
@@ -10569,9 +10583,9 @@
       <c r="K257" t="s">
         <v>29</v>
       </c>
-      <c r="L257" s="2" t="e">
+      <c r="L257" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40257.746884249776</v>
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.3">
@@ -10608,9 +10622,9 @@
       <c r="K258" t="s">
         <v>43</v>
       </c>
-      <c r="L258" s="2" t="e">
+      <c r="L258" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41694.60425669518</v>
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.3">
@@ -10647,9 +10661,9 @@
       <c r="K259" t="s">
         <v>23</v>
       </c>
-      <c r="L259" s="2" t="e">
+      <c r="L259" s="2">
         <f t="shared" ref="L259:L322" ca="1" si="4">(RAND()*("14/01/2016"-"14/01/2010"+1))+"14/01/2010"</f>
-        <v>#VALUE!</v>
+        <v>41329.490114396838</v>
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.3">
@@ -10686,9 +10700,9 @@
       <c r="K260" t="s">
         <v>29</v>
       </c>
-      <c r="L260" s="2" t="e">
+      <c r="L260" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41514.144184931778</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.3">
@@ -10725,9 +10739,9 @@
       <c r="K261" t="s">
         <v>29</v>
       </c>
-      <c r="L261" s="2" t="e">
+      <c r="L261" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42281.834535224058</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.3">
@@ -10764,9 +10778,9 @@
       <c r="K262" t="s">
         <v>17</v>
       </c>
-      <c r="L262" s="2" t="e">
+      <c r="L262" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40547.262280546252</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.3">
@@ -10803,9 +10817,9 @@
       <c r="K263" t="s">
         <v>35</v>
       </c>
-      <c r="L263" s="2" t="e">
+      <c r="L263" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40275.374807045147</v>
       </c>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.3">
@@ -10842,9 +10856,9 @@
       <c r="K264" t="s">
         <v>35</v>
       </c>
-      <c r="L264" s="2" t="e">
+      <c r="L264" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41835.004161762714</v>
       </c>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.3">
@@ -10881,9 +10895,9 @@
       <c r="K265" t="s">
         <v>35</v>
       </c>
-      <c r="L265" s="2" t="e">
+      <c r="L265" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40680.727868996037</v>
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.3">
@@ -10920,9 +10934,9 @@
       <c r="K266" t="s">
         <v>23</v>
       </c>
-      <c r="L266" s="2" t="e">
+      <c r="L266" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40651.815998644073</v>
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.3">
@@ -10959,9 +10973,9 @@
       <c r="K267" t="s">
         <v>29</v>
       </c>
-      <c r="L267" s="2" t="e">
+      <c r="L267" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40204.88746253428</v>
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.3">
@@ -10998,9 +11012,9 @@
       <c r="K268" t="s">
         <v>20</v>
       </c>
-      <c r="L268" s="2" t="e">
+      <c r="L268" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41220.43903301777</v>
       </c>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.3">
@@ -11037,9 +11051,9 @@
       <c r="K269" t="s">
         <v>17</v>
       </c>
-      <c r="L269" s="2" t="e">
+      <c r="L269" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40619.805921769454</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.3">
@@ -11076,9 +11090,9 @@
       <c r="K270" t="s">
         <v>17</v>
       </c>
-      <c r="L270" s="2" t="e">
+      <c r="L270" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41771.630168676609</v>
       </c>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.3">
@@ -11115,9 +11129,9 @@
       <c r="K271" t="s">
         <v>54</v>
       </c>
-      <c r="L271" s="2" t="e">
+      <c r="L271" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41921.619615903161</v>
       </c>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.3">
@@ -11154,9 +11168,9 @@
       <c r="K272" t="s">
         <v>17</v>
       </c>
-      <c r="L272" s="2" t="e">
+      <c r="L272" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40531.275783183715</v>
       </c>
     </row>
     <row r="273" spans="1:12" x14ac:dyDescent="0.3">
@@ -11193,9 +11207,9 @@
       <c r="K273" t="s">
         <v>35</v>
       </c>
-      <c r="L273" s="2" t="e">
+      <c r="L273" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41665.842912129032</v>
       </c>
     </row>
     <row r="274" spans="1:12" x14ac:dyDescent="0.3">
@@ -11232,9 +11246,9 @@
       <c r="K274" t="s">
         <v>23</v>
       </c>
-      <c r="L274" s="2" t="e">
+      <c r="L274" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41787.386283885571</v>
       </c>
     </row>
     <row r="275" spans="1:12" x14ac:dyDescent="0.3">
@@ -11271,9 +11285,9 @@
       <c r="K275" t="s">
         <v>23</v>
       </c>
-      <c r="L275" s="2" t="e">
+      <c r="L275" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41388.272205454123</v>
       </c>
     </row>
     <row r="276" spans="1:12" x14ac:dyDescent="0.3">
@@ -11310,9 +11324,9 @@
       <c r="K276" t="s">
         <v>20</v>
       </c>
-      <c r="L276" s="2" t="e">
+      <c r="L276" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40514.133090272633</v>
       </c>
     </row>
     <row r="277" spans="1:12" x14ac:dyDescent="0.3">
@@ -11349,9 +11363,9 @@
       <c r="K277" t="s">
         <v>29</v>
       </c>
-      <c r="L277" s="2" t="e">
+      <c r="L277" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41044.332310747217</v>
       </c>
     </row>
     <row r="278" spans="1:12" x14ac:dyDescent="0.3">
@@ -11388,9 +11402,9 @@
       <c r="K278" t="s">
         <v>29</v>
       </c>
-      <c r="L278" s="2" t="e">
+      <c r="L278" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40256.033235019415</v>
       </c>
     </row>
     <row r="279" spans="1:12" x14ac:dyDescent="0.3">
@@ -11427,9 +11441,9 @@
       <c r="K279" t="s">
         <v>17</v>
       </c>
-      <c r="L279" s="2" t="e">
+      <c r="L279" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40280.961241746896</v>
       </c>
     </row>
     <row r="280" spans="1:12" x14ac:dyDescent="0.3">
@@ -11466,9 +11480,9 @@
       <c r="K280" t="s">
         <v>14</v>
       </c>
-      <c r="L280" s="2" t="e">
+      <c r="L280" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40691.361065607729</v>
       </c>
     </row>
     <row r="281" spans="1:12" x14ac:dyDescent="0.3">
@@ -11505,9 +11519,9 @@
       <c r="K281" t="s">
         <v>14</v>
       </c>
-      <c r="L281" s="2" t="e">
+      <c r="L281" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40451.115887102198</v>
       </c>
     </row>
     <row r="282" spans="1:12" x14ac:dyDescent="0.3">
@@ -11544,9 +11558,9 @@
       <c r="K282" t="s">
         <v>17</v>
       </c>
-      <c r="L282" s="2" t="e">
+      <c r="L282" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40736.756849502664</v>
       </c>
     </row>
     <row r="283" spans="1:12" x14ac:dyDescent="0.3">
@@ -11583,9 +11597,9 @@
       <c r="K283" t="s">
         <v>29</v>
       </c>
-      <c r="L283" s="2" t="e">
+      <c r="L283" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40543.820782147362</v>
       </c>
     </row>
     <row r="284" spans="1:12" x14ac:dyDescent="0.3">
@@ -11622,9 +11636,9 @@
       <c r="K284" t="s">
         <v>23</v>
       </c>
-      <c r="L284" s="2" t="e">
+      <c r="L284" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42045.996740007664</v>
       </c>
     </row>
     <row r="285" spans="1:12" x14ac:dyDescent="0.3">
@@ -11661,9 +11675,9 @@
       <c r="K285" t="s">
         <v>35</v>
       </c>
-      <c r="L285" s="2" t="e">
+      <c r="L285" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42169.814645288323</v>
       </c>
     </row>
     <row r="286" spans="1:12" x14ac:dyDescent="0.3">
@@ -11700,9 +11714,9 @@
       <c r="K286" t="s">
         <v>23</v>
       </c>
-      <c r="L286" s="2" t="e">
+      <c r="L286" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42089.500812045415</v>
       </c>
     </row>
     <row r="287" spans="1:12" x14ac:dyDescent="0.3">
@@ -11739,9 +11753,9 @@
       <c r="K287" t="s">
         <v>17</v>
       </c>
-      <c r="L287" s="2" t="e">
+      <c r="L287" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42159.644952218376</v>
       </c>
     </row>
     <row r="288" spans="1:12" x14ac:dyDescent="0.3">
@@ -11778,9 +11792,9 @@
       <c r="K288" t="s">
         <v>37</v>
       </c>
-      <c r="L288" s="2" t="e">
+      <c r="L288" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41974.856648004708</v>
       </c>
     </row>
     <row r="289" spans="1:12" x14ac:dyDescent="0.3">
@@ -11817,9 +11831,9 @@
       <c r="K289" t="s">
         <v>29</v>
       </c>
-      <c r="L289" s="2" t="e">
+      <c r="L289" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42084.042431003276</v>
       </c>
     </row>
     <row r="290" spans="1:12" x14ac:dyDescent="0.3">
@@ -11856,9 +11870,9 @@
       <c r="K290" t="s">
         <v>54</v>
       </c>
-      <c r="L290" s="2" t="e">
+      <c r="L290" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41522.567419710169</v>
       </c>
     </row>
     <row r="291" spans="1:12" x14ac:dyDescent="0.3">
@@ -11895,9 +11909,9 @@
       <c r="K291" t="s">
         <v>37</v>
       </c>
-      <c r="L291" s="2" t="e">
+      <c r="L291" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40767.161188211052</v>
       </c>
     </row>
     <row r="292" spans="1:12" x14ac:dyDescent="0.3">
@@ -11934,9 +11948,9 @@
       <c r="K292" t="s">
         <v>23</v>
       </c>
-      <c r="L292" s="2" t="e">
+      <c r="L292" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40348.672546320777</v>
       </c>
     </row>
     <row r="293" spans="1:12" x14ac:dyDescent="0.3">
@@ -11973,9 +11987,9 @@
       <c r="K293" t="s">
         <v>43</v>
       </c>
-      <c r="L293" s="2" t="e">
+      <c r="L293" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42071.8626791598</v>
       </c>
     </row>
     <row r="294" spans="1:12" x14ac:dyDescent="0.3">
@@ -12012,9 +12026,9 @@
       <c r="K294" t="s">
         <v>20</v>
       </c>
-      <c r="L294" s="2" t="e">
+      <c r="L294" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40973.574786554105</v>
       </c>
     </row>
     <row r="295" spans="1:12" x14ac:dyDescent="0.3">
@@ -12051,9 +12065,9 @@
       <c r="K295" t="s">
         <v>54</v>
       </c>
-      <c r="L295" s="2" t="e">
+      <c r="L295" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40631.487480220108</v>
       </c>
     </row>
     <row r="296" spans="1:12" x14ac:dyDescent="0.3">
@@ -12090,9 +12104,9 @@
       <c r="K296" t="s">
         <v>23</v>
       </c>
-      <c r="L296" s="2" t="e">
+      <c r="L296" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40703.08136648425</v>
       </c>
     </row>
     <row r="297" spans="1:12" x14ac:dyDescent="0.3">
@@ -12129,9 +12143,9 @@
       <c r="K297" t="s">
         <v>37</v>
       </c>
-      <c r="L297" s="2" t="e">
+      <c r="L297" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42338.533112542958</v>
       </c>
     </row>
     <row r="298" spans="1:12" x14ac:dyDescent="0.3">
@@ -12168,9 +12182,9 @@
       <c r="K298" t="s">
         <v>32</v>
       </c>
-      <c r="L298" s="2" t="e">
+      <c r="L298" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42232.850232200326</v>
       </c>
     </row>
     <row r="299" spans="1:12" x14ac:dyDescent="0.3">
@@ -12207,9 +12221,9 @@
       <c r="K299" t="s">
         <v>20</v>
       </c>
-      <c r="L299" s="2" t="e">
+      <c r="L299" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40420.579636086644</v>
       </c>
     </row>
     <row r="300" spans="1:12" x14ac:dyDescent="0.3">
@@ -12246,9 +12260,9 @@
       <c r="K300" t="s">
         <v>54</v>
       </c>
-      <c r="L300" s="2" t="e">
+      <c r="L300" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41149.288572028636</v>
       </c>
     </row>
     <row r="301" spans="1:12" x14ac:dyDescent="0.3">
@@ -12285,9 +12299,9 @@
       <c r="K301" t="s">
         <v>17</v>
       </c>
-      <c r="L301" s="2" t="e">
+      <c r="L301" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40898.703212031171</v>
       </c>
     </row>
     <row r="302" spans="1:12" x14ac:dyDescent="0.3">
@@ -12324,9 +12338,9 @@
       <c r="K302" t="s">
         <v>29</v>
       </c>
-      <c r="L302" s="2" t="e">
+      <c r="L302" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41646.458923447513</v>
       </c>
     </row>
     <row r="303" spans="1:12" x14ac:dyDescent="0.3">
@@ -12363,9 +12377,9 @@
       <c r="K303" t="s">
         <v>32</v>
       </c>
-      <c r="L303" s="2" t="e">
+      <c r="L303" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41875.030621200378</v>
       </c>
     </row>
     <row r="304" spans="1:12" x14ac:dyDescent="0.3">
@@ -12402,9 +12416,9 @@
       <c r="K304" t="s">
         <v>43</v>
       </c>
-      <c r="L304" s="2" t="e">
+      <c r="L304" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40313.90714753767</v>
       </c>
     </row>
     <row r="305" spans="1:12" x14ac:dyDescent="0.3">
@@ -12441,9 +12455,9 @@
       <c r="K305" t="s">
         <v>14</v>
       </c>
-      <c r="L305" s="2" t="e">
+      <c r="L305" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40499.155058114091</v>
       </c>
     </row>
     <row r="306" spans="1:12" x14ac:dyDescent="0.3">
@@ -12480,9 +12494,9 @@
       <c r="K306" t="s">
         <v>43</v>
       </c>
-      <c r="L306" s="2" t="e">
+      <c r="L306" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41709.461482188934</v>
       </c>
     </row>
     <row r="307" spans="1:12" x14ac:dyDescent="0.3">
@@ -12519,9 +12533,9 @@
       <c r="K307" t="s">
         <v>17</v>
       </c>
-      <c r="L307" s="2" t="e">
+      <c r="L307" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41225.375064242056</v>
       </c>
     </row>
     <row r="308" spans="1:12" x14ac:dyDescent="0.3">
@@ -12558,9 +12572,9 @@
       <c r="K308" t="s">
         <v>29</v>
       </c>
-      <c r="L308" s="2" t="e">
+      <c r="L308" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40951.477831969562</v>
       </c>
     </row>
     <row r="309" spans="1:12" x14ac:dyDescent="0.3">
@@ -12597,9 +12611,9 @@
       <c r="K309" t="s">
         <v>37</v>
       </c>
-      <c r="L309" s="2" t="e">
+      <c r="L309" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42067.451282347261</v>
       </c>
     </row>
     <row r="310" spans="1:12" x14ac:dyDescent="0.3">
@@ -12636,9 +12650,9 @@
       <c r="K310" t="s">
         <v>35</v>
       </c>
-      <c r="L310" s="2" t="e">
+      <c r="L310" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42363.890610847178</v>
       </c>
     </row>
     <row r="311" spans="1:12" x14ac:dyDescent="0.3">
@@ -12675,9 +12689,9 @@
       <c r="K311" t="s">
         <v>35</v>
       </c>
-      <c r="L311" s="2" t="e">
+      <c r="L311" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40215.965668573226</v>
       </c>
     </row>
     <row r="312" spans="1:12" x14ac:dyDescent="0.3">
@@ -12714,9 +12728,9 @@
       <c r="K312" t="s">
         <v>29</v>
       </c>
-      <c r="L312" s="2" t="e">
+      <c r="L312" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41576.10702013503</v>
       </c>
     </row>
     <row r="313" spans="1:12" x14ac:dyDescent="0.3">
@@ -12753,9 +12767,9 @@
       <c r="K313" t="s">
         <v>32</v>
       </c>
-      <c r="L313" s="2" t="e">
+      <c r="L313" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42190.741231060252</v>
       </c>
     </row>
     <row r="314" spans="1:12" x14ac:dyDescent="0.3">
@@ -12792,9 +12806,9 @@
       <c r="K314" t="s">
         <v>20</v>
       </c>
-      <c r="L314" s="2" t="e">
+      <c r="L314" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42180.21584179427</v>
       </c>
     </row>
     <row r="315" spans="1:12" x14ac:dyDescent="0.3">
@@ -12831,9 +12845,9 @@
       <c r="K315" t="s">
         <v>35</v>
       </c>
-      <c r="L315" s="2" t="e">
+      <c r="L315" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41697.41134529985</v>
       </c>
     </row>
     <row r="316" spans="1:12" x14ac:dyDescent="0.3">
@@ -12870,9 +12884,9 @@
       <c r="K316" t="s">
         <v>43</v>
       </c>
-      <c r="L316" s="2" t="e">
+      <c r="L316" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40312.042718607285</v>
       </c>
     </row>
     <row r="317" spans="1:12" x14ac:dyDescent="0.3">
@@ -12909,9 +12923,9 @@
       <c r="K317" t="s">
         <v>37</v>
       </c>
-      <c r="L317" s="2" t="e">
+      <c r="L317" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41068.737870885787</v>
       </c>
     </row>
     <row r="318" spans="1:12" x14ac:dyDescent="0.3">
@@ -12948,9 +12962,9 @@
       <c r="K318" t="s">
         <v>20</v>
       </c>
-      <c r="L318" s="2" t="e">
+      <c r="L318" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40655.992809583418</v>
       </c>
     </row>
     <row r="319" spans="1:12" x14ac:dyDescent="0.3">
@@ -12987,9 +13001,9 @@
       <c r="K319" t="s">
         <v>35</v>
       </c>
-      <c r="L319" s="2" t="e">
+      <c r="L319" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41712.00347869633</v>
       </c>
     </row>
     <row r="320" spans="1:12" x14ac:dyDescent="0.3">
@@ -13026,9 +13040,9 @@
       <c r="K320" t="s">
         <v>43</v>
       </c>
-      <c r="L320" s="2" t="e">
+      <c r="L320" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41960.135963347464</v>
       </c>
     </row>
     <row r="321" spans="1:12" x14ac:dyDescent="0.3">
@@ -13065,9 +13079,9 @@
       <c r="K321" t="s">
         <v>14</v>
       </c>
-      <c r="L321" s="2" t="e">
+      <c r="L321" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41213.240150004523</v>
       </c>
     </row>
     <row r="322" spans="1:12" x14ac:dyDescent="0.3">
@@ -13104,9 +13118,9 @@
       <c r="K322" t="s">
         <v>17</v>
       </c>
-      <c r="L322" s="2" t="e">
+      <c r="L322" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41969.78788713798</v>
       </c>
     </row>
     <row r="323" spans="1:12" x14ac:dyDescent="0.3">
@@ -13143,9 +13157,9 @@
       <c r="K323" t="s">
         <v>37</v>
       </c>
-      <c r="L323" s="2" t="e">
+      <c r="L323" s="2">
         <f t="shared" ref="L323:L386" ca="1" si="5">(RAND()*("14/01/2016"-"14/01/2010"+1))+"14/01/2010"</f>
-        <v>#VALUE!</v>
+        <v>42312.370838925308</v>
       </c>
     </row>
     <row r="324" spans="1:12" x14ac:dyDescent="0.3">
@@ -13182,9 +13196,9 @@
       <c r="K324" t="s">
         <v>43</v>
       </c>
-      <c r="L324" s="2" t="e">
+      <c r="L324" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41837.457156140226</v>
       </c>
     </row>
     <row r="325" spans="1:12" x14ac:dyDescent="0.3">
@@ -13221,9 +13235,9 @@
       <c r="K325" t="s">
         <v>17</v>
       </c>
-      <c r="L325" s="2" t="e">
+      <c r="L325" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40899.930626703419</v>
       </c>
     </row>
     <row r="326" spans="1:12" x14ac:dyDescent="0.3">
@@ -13260,9 +13274,9 @@
       <c r="K326" t="s">
         <v>29</v>
       </c>
-      <c r="L326" s="2" t="e">
+      <c r="L326" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41867.294808091865</v>
       </c>
     </row>
     <row r="327" spans="1:12" x14ac:dyDescent="0.3">
@@ -13299,9 +13313,9 @@
       <c r="K327" t="s">
         <v>14</v>
       </c>
-      <c r="L327" s="2" t="e">
+      <c r="L327" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42163.513198728746</v>
       </c>
     </row>
     <row r="328" spans="1:12" x14ac:dyDescent="0.3">
@@ -13338,9 +13352,9 @@
       <c r="K328" t="s">
         <v>29</v>
       </c>
-      <c r="L328" s="2" t="e">
+      <c r="L328" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41015.206927183361</v>
       </c>
     </row>
     <row r="329" spans="1:12" x14ac:dyDescent="0.3">
@@ -13377,9 +13391,9 @@
       <c r="K329" t="s">
         <v>14</v>
       </c>
-      <c r="L329" s="2" t="e">
+      <c r="L329" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42107.90569645651</v>
       </c>
     </row>
     <row r="330" spans="1:12" x14ac:dyDescent="0.3">
@@ -13416,9 +13430,9 @@
       <c r="K330" t="s">
         <v>20</v>
       </c>
-      <c r="L330" s="2" t="e">
+      <c r="L330" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40396.67654297196</v>
       </c>
     </row>
     <row r="331" spans="1:12" x14ac:dyDescent="0.3">
@@ -13455,9 +13469,9 @@
       <c r="K331" t="s">
         <v>29</v>
       </c>
-      <c r="L331" s="2" t="e">
+      <c r="L331" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41835.011398440925</v>
       </c>
     </row>
     <row r="332" spans="1:12" x14ac:dyDescent="0.3">
@@ -13494,9 +13508,9 @@
       <c r="K332" t="s">
         <v>20</v>
       </c>
-      <c r="L332" s="2" t="e">
+      <c r="L332" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42321.585547029856</v>
       </c>
     </row>
     <row r="333" spans="1:12" x14ac:dyDescent="0.3">
@@ -13533,9 +13547,9 @@
       <c r="K333" t="s">
         <v>14</v>
       </c>
-      <c r="L333" s="2" t="e">
+      <c r="L333" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41609.133104817229</v>
       </c>
     </row>
     <row r="334" spans="1:12" x14ac:dyDescent="0.3">
@@ -13572,9 +13586,9 @@
       <c r="K334" t="s">
         <v>14</v>
       </c>
-      <c r="L334" s="2" t="e">
+      <c r="L334" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41658.207349721029</v>
       </c>
     </row>
     <row r="335" spans="1:12" x14ac:dyDescent="0.3">
@@ -13611,9 +13625,9 @@
       <c r="K335" t="s">
         <v>23</v>
       </c>
-      <c r="L335" s="2" t="e">
+      <c r="L335" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42017.416872608097</v>
       </c>
     </row>
     <row r="336" spans="1:12" x14ac:dyDescent="0.3">
@@ -13650,9 +13664,9 @@
       <c r="K336" t="s">
         <v>43</v>
       </c>
-      <c r="L336" s="2" t="e">
+      <c r="L336" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41439.888456223875</v>
       </c>
     </row>
     <row r="337" spans="1:12" x14ac:dyDescent="0.3">
@@ -13689,9 +13703,9 @@
       <c r="K337" t="s">
         <v>14</v>
       </c>
-      <c r="L337" s="2" t="e">
+      <c r="L337" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41361.007819723854</v>
       </c>
     </row>
     <row r="338" spans="1:12" x14ac:dyDescent="0.3">
@@ -13728,9 +13742,9 @@
       <c r="K338" t="s">
         <v>35</v>
       </c>
-      <c r="L338" s="2" t="e">
+      <c r="L338" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41524.628459261854</v>
       </c>
     </row>
     <row r="339" spans="1:12" x14ac:dyDescent="0.3">
@@ -13767,9 +13781,9 @@
       <c r="K339" t="s">
         <v>14</v>
       </c>
-      <c r="L339" s="2" t="e">
+      <c r="L339" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41726.993205528692</v>
       </c>
     </row>
     <row r="340" spans="1:12" x14ac:dyDescent="0.3">
@@ -13806,9 +13820,9 @@
       <c r="K340" t="s">
         <v>17</v>
       </c>
-      <c r="L340" s="2" t="e">
+      <c r="L340" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41648.211230943918</v>
       </c>
     </row>
     <row r="341" spans="1:12" x14ac:dyDescent="0.3">
@@ -13845,9 +13859,9 @@
       <c r="K341" t="s">
         <v>54</v>
       </c>
-      <c r="L341" s="2" t="e">
+      <c r="L341" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42140.881234270841</v>
       </c>
     </row>
     <row r="342" spans="1:12" x14ac:dyDescent="0.3">
@@ -13884,9 +13898,9 @@
       <c r="K342" t="s">
         <v>14</v>
       </c>
-      <c r="L342" s="2" t="e">
+      <c r="L342" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42226.252664450069</v>
       </c>
     </row>
     <row r="343" spans="1:12" x14ac:dyDescent="0.3">
@@ -13923,9 +13937,9 @@
       <c r="K343" t="s">
         <v>37</v>
       </c>
-      <c r="L343" s="2" t="e">
+      <c r="L343" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42085.744379348791</v>
       </c>
     </row>
     <row r="344" spans="1:12" x14ac:dyDescent="0.3">
@@ -13962,9 +13976,9 @@
       <c r="K344" t="s">
         <v>43</v>
       </c>
-      <c r="L344" s="2" t="e">
+      <c r="L344" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41136.736104163356</v>
       </c>
     </row>
     <row r="345" spans="1:12" x14ac:dyDescent="0.3">
@@ -14001,9 +14015,9 @@
       <c r="K345" t="s">
         <v>37</v>
       </c>
-      <c r="L345" s="2" t="e">
+      <c r="L345" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40570.950740600856</v>
       </c>
     </row>
     <row r="346" spans="1:12" x14ac:dyDescent="0.3">
@@ -14040,9 +14054,9 @@
       <c r="K346" t="s">
         <v>20</v>
       </c>
-      <c r="L346" s="2" t="e">
+      <c r="L346" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40989.437861202445</v>
       </c>
     </row>
     <row r="347" spans="1:12" x14ac:dyDescent="0.3">
@@ -14079,9 +14093,9 @@
       <c r="K347" t="s">
         <v>17</v>
       </c>
-      <c r="L347" s="2" t="e">
+      <c r="L347" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41856.671601564754</v>
       </c>
     </row>
     <row r="348" spans="1:12" x14ac:dyDescent="0.3">
@@ -14118,9 +14132,9 @@
       <c r="K348" t="s">
         <v>35</v>
       </c>
-      <c r="L348" s="2" t="e">
+      <c r="L348" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41434.552220378158</v>
       </c>
     </row>
     <row r="349" spans="1:12" x14ac:dyDescent="0.3">
@@ -14157,9 +14171,9 @@
       <c r="K349" t="s">
         <v>17</v>
       </c>
-      <c r="L349" s="2" t="e">
+      <c r="L349" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42066.162660360998</v>
       </c>
     </row>
     <row r="350" spans="1:12" x14ac:dyDescent="0.3">
@@ -14196,9 +14210,9 @@
       <c r="K350" t="s">
         <v>17</v>
       </c>
-      <c r="L350" s="2" t="e">
+      <c r="L350" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40759.559966197463</v>
       </c>
     </row>
     <row r="351" spans="1:12" x14ac:dyDescent="0.3">
@@ -14235,9 +14249,9 @@
       <c r="K351" t="s">
         <v>29</v>
       </c>
-      <c r="L351" s="2" t="e">
+      <c r="L351" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41600.173529126587</v>
       </c>
     </row>
     <row r="352" spans="1:12" x14ac:dyDescent="0.3">
@@ -14274,9 +14288,9 @@
       <c r="K352" t="s">
         <v>20</v>
       </c>
-      <c r="L352" s="2" t="e">
+      <c r="L352" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40587.985821693852</v>
       </c>
     </row>
     <row r="353" spans="1:12" x14ac:dyDescent="0.3">
@@ -14313,9 +14327,9 @@
       <c r="K353" t="s">
         <v>37</v>
       </c>
-      <c r="L353" s="2" t="e">
+      <c r="L353" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40828.936334388549</v>
       </c>
     </row>
     <row r="354" spans="1:12" x14ac:dyDescent="0.3">
@@ -14352,9 +14366,9 @@
       <c r="K354" t="s">
         <v>20</v>
       </c>
-      <c r="L354" s="2" t="e">
+      <c r="L354" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41897.915958000973</v>
       </c>
     </row>
     <row r="355" spans="1:12" x14ac:dyDescent="0.3">
@@ -14391,9 +14405,9 @@
       <c r="K355" t="s">
         <v>23</v>
       </c>
-      <c r="L355" s="2" t="e">
+      <c r="L355" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41351.485086040571</v>
       </c>
     </row>
     <row r="356" spans="1:12" x14ac:dyDescent="0.3">
@@ -14430,9 +14444,9 @@
       <c r="K356" t="s">
         <v>37</v>
       </c>
-      <c r="L356" s="2" t="e">
+      <c r="L356" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41122.78380048721</v>
       </c>
     </row>
     <row r="357" spans="1:12" x14ac:dyDescent="0.3">
@@ -14469,9 +14483,9 @@
       <c r="K357" t="s">
         <v>37</v>
       </c>
-      <c r="L357" s="2" t="e">
+      <c r="L357" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41976.546541963704</v>
       </c>
     </row>
     <row r="358" spans="1:12" x14ac:dyDescent="0.3">
@@ -14508,9 +14522,9 @@
       <c r="K358" t="s">
         <v>32</v>
       </c>
-      <c r="L358" s="2" t="e">
+      <c r="L358" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40485.174887730915</v>
       </c>
     </row>
     <row r="359" spans="1:12" x14ac:dyDescent="0.3">
@@ -14547,9 +14561,9 @@
       <c r="K359" t="s">
         <v>20</v>
       </c>
-      <c r="L359" s="2" t="e">
+      <c r="L359" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41470.822790042352</v>
       </c>
     </row>
     <row r="360" spans="1:12" x14ac:dyDescent="0.3">
@@ -14586,9 +14600,9 @@
       <c r="K360" t="s">
         <v>29</v>
       </c>
-      <c r="L360" s="2" t="e">
+      <c r="L360" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42196.186733585171</v>
       </c>
     </row>
     <row r="361" spans="1:12" x14ac:dyDescent="0.3">
@@ -14625,9 +14639,9 @@
       <c r="K361" t="s">
         <v>14</v>
       </c>
-      <c r="L361" s="2" t="e">
+      <c r="L361" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41789.703050668111</v>
       </c>
     </row>
     <row r="362" spans="1:12" x14ac:dyDescent="0.3">
@@ -14664,9 +14678,9 @@
       <c r="K362" t="s">
         <v>35</v>
       </c>
-      <c r="L362" s="2" t="e">
+      <c r="L362" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40706.213870013315</v>
       </c>
     </row>
     <row r="363" spans="1:12" x14ac:dyDescent="0.3">
@@ -14703,9 +14717,9 @@
       <c r="K363" t="s">
         <v>37</v>
       </c>
-      <c r="L363" s="2" t="e">
+      <c r="L363" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41040.215905033205</v>
       </c>
     </row>
     <row r="364" spans="1:12" x14ac:dyDescent="0.3">
@@ -14742,9 +14756,9 @@
       <c r="K364" t="s">
         <v>32</v>
       </c>
-      <c r="L364" s="2" t="e">
+      <c r="L364" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40541.759417992449</v>
       </c>
     </row>
     <row r="365" spans="1:12" x14ac:dyDescent="0.3">
@@ -14781,9 +14795,9 @@
       <c r="K365" t="s">
         <v>14</v>
       </c>
-      <c r="L365" s="2" t="e">
+      <c r="L365" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42350.583440613002</v>
       </c>
     </row>
     <row r="366" spans="1:12" x14ac:dyDescent="0.3">
@@ -14820,9 +14834,9 @@
       <c r="K366" t="s">
         <v>43</v>
       </c>
-      <c r="L366" s="2" t="e">
+      <c r="L366" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42314.186175800343</v>
       </c>
     </row>
     <row r="367" spans="1:12" x14ac:dyDescent="0.3">
@@ -14859,9 +14873,9 @@
       <c r="K367" t="s">
         <v>54</v>
       </c>
-      <c r="L367" s="2" t="e">
+      <c r="L367" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41827.625230233789</v>
       </c>
     </row>
     <row r="368" spans="1:12" x14ac:dyDescent="0.3">
@@ -14898,9 +14912,9 @@
       <c r="K368" t="s">
         <v>14</v>
       </c>
-      <c r="L368" s="2" t="e">
+      <c r="L368" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40594.98001062082</v>
       </c>
     </row>
     <row r="369" spans="1:12" x14ac:dyDescent="0.3">
@@ -14937,9 +14951,9 @@
       <c r="K369" t="s">
         <v>17</v>
       </c>
-      <c r="L369" s="2" t="e">
+      <c r="L369" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41484.637635341292</v>
       </c>
     </row>
     <row r="370" spans="1:12" x14ac:dyDescent="0.3">
@@ -14976,9 +14990,9 @@
       <c r="K370" t="s">
         <v>54</v>
       </c>
-      <c r="L370" s="2" t="e">
+      <c r="L370" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40960.940199485922</v>
       </c>
     </row>
     <row r="371" spans="1:12" x14ac:dyDescent="0.3">
@@ -15015,9 +15029,9 @@
       <c r="K371" t="s">
         <v>43</v>
       </c>
-      <c r="L371" s="2" t="e">
+      <c r="L371" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42033.505236589161</v>
       </c>
     </row>
     <row r="372" spans="1:12" x14ac:dyDescent="0.3">
@@ -15054,9 +15068,9 @@
       <c r="K372" t="s">
         <v>35</v>
       </c>
-      <c r="L372" s="2" t="e">
+      <c r="L372" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41114.705267453224</v>
       </c>
     </row>
     <row r="373" spans="1:12" x14ac:dyDescent="0.3">
@@ -15093,9 +15107,9 @@
       <c r="K373" t="s">
         <v>20</v>
       </c>
-      <c r="L373" s="2" t="e">
+      <c r="L373" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41412.975559321167</v>
       </c>
     </row>
     <row r="374" spans="1:12" x14ac:dyDescent="0.3">
@@ -15132,9 +15146,9 @@
       <c r="K374" t="s">
         <v>43</v>
       </c>
-      <c r="L374" s="2" t="e">
+      <c r="L374" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40526.471797288563</v>
       </c>
     </row>
     <row r="375" spans="1:12" x14ac:dyDescent="0.3">
@@ -15171,9 +15185,9 @@
       <c r="K375" t="s">
         <v>54</v>
       </c>
-      <c r="L375" s="2" t="e">
+      <c r="L375" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42350.121726415535</v>
       </c>
     </row>
     <row r="376" spans="1:12" x14ac:dyDescent="0.3">
@@ -15210,9 +15224,9 @@
       <c r="K376" t="s">
         <v>37</v>
       </c>
-      <c r="L376" s="2" t="e">
+      <c r="L376" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41481.201890102813</v>
       </c>
     </row>
     <row r="377" spans="1:12" x14ac:dyDescent="0.3">
@@ -15249,9 +15263,9 @@
       <c r="K377" t="s">
         <v>43</v>
       </c>
-      <c r="L377" s="2" t="e">
+      <c r="L377" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42003.923926970441</v>
       </c>
     </row>
     <row r="378" spans="1:12" x14ac:dyDescent="0.3">
@@ -15288,9 +15302,9 @@
       <c r="K378" t="s">
         <v>14</v>
       </c>
-      <c r="L378" s="2" t="e">
+      <c r="L378" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40446.245769769434</v>
       </c>
     </row>
     <row r="379" spans="1:12" x14ac:dyDescent="0.3">
@@ -15327,9 +15341,9 @@
       <c r="K379" t="s">
         <v>43</v>
       </c>
-      <c r="L379" s="2" t="e">
+      <c r="L379" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41281.855020092997</v>
       </c>
     </row>
     <row r="380" spans="1:12" x14ac:dyDescent="0.3">
@@ -15366,9 +15380,9 @@
       <c r="K380" t="s">
         <v>37</v>
       </c>
-      <c r="L380" s="2" t="e">
+      <c r="L380" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40782.110056732563</v>
       </c>
     </row>
     <row r="381" spans="1:12" x14ac:dyDescent="0.3">
@@ -15405,9 +15419,9 @@
       <c r="K381" t="s">
         <v>32</v>
       </c>
-      <c r="L381" s="2" t="e">
+      <c r="L381" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41565.754772802677</v>
       </c>
     </row>
     <row r="382" spans="1:12" x14ac:dyDescent="0.3">
@@ -15444,9 +15458,9 @@
       <c r="K382" t="s">
         <v>14</v>
       </c>
-      <c r="L382" s="2" t="e">
+      <c r="L382" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42176.649664049895</v>
       </c>
     </row>
     <row r="383" spans="1:12" x14ac:dyDescent="0.3">
@@ -15483,9 +15497,9 @@
       <c r="K383" t="s">
         <v>20</v>
       </c>
-      <c r="L383" s="2" t="e">
+      <c r="L383" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41516.796489874876</v>
       </c>
     </row>
     <row r="384" spans="1:12" x14ac:dyDescent="0.3">
@@ -15522,9 +15536,9 @@
       <c r="K384" t="s">
         <v>17</v>
       </c>
-      <c r="L384" s="2" t="e">
+      <c r="L384" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41158.848108120001</v>
       </c>
     </row>
     <row r="385" spans="1:12" x14ac:dyDescent="0.3">
@@ -15561,9 +15575,9 @@
       <c r="K385" t="s">
         <v>14</v>
       </c>
-      <c r="L385" s="2" t="e">
+      <c r="L385" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41584.627947870184</v>
       </c>
     </row>
     <row r="386" spans="1:12" x14ac:dyDescent="0.3">
@@ -15600,9 +15614,9 @@
       <c r="K386" t="s">
         <v>32</v>
       </c>
-      <c r="L386" s="2" t="e">
+      <c r="L386" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41720.629455080765</v>
       </c>
     </row>
     <row r="387" spans="1:12" x14ac:dyDescent="0.3">
@@ -15639,9 +15653,9 @@
       <c r="K387" t="s">
         <v>43</v>
       </c>
-      <c r="L387" s="2" t="e">
+      <c r="L387" s="2">
         <f ca="1">(RAND()*("14/01/2016"-"14/01/2010"+1))+"14/01/2010"</f>
-        <v>#VALUE!</v>
+        <v>40969.561271684201</v>
       </c>
     </row>
     <row r="388" spans="1:12" x14ac:dyDescent="0.3">
@@ -15678,9 +15692,9 @@
       <c r="K388" t="s">
         <v>32</v>
       </c>
-      <c r="L388" s="2" t="e">
+      <c r="L388" s="2">
         <f ca="1">(RAND()*("14/01/2016"-"14/01/2010"+1))+"14/01/2010"</f>
-        <v>#VALUE!</v>
+        <v>40282.781902079791</v>
       </c>
     </row>
     <row r="389" spans="1:12" x14ac:dyDescent="0.3">
@@ -15717,9 +15731,9 @@
       <c r="K389" t="s">
         <v>35</v>
       </c>
-      <c r="L389" s="2" t="e">
+      <c r="L389" s="2">
         <f ca="1">(RAND()*("14/01/2016"-"14/01/2010"+1))+"14/01/2010"</f>
-        <v>#VALUE!</v>
+        <v>41524.715147510935</v>
       </c>
     </row>
     <row r="390" spans="1:12" x14ac:dyDescent="0.3">
@@ -15756,9 +15770,9 @@
       <c r="K390" t="s">
         <v>20</v>
       </c>
-      <c r="L390" s="2" t="e">
+      <c r="L390" s="2">
         <f ca="1">(RAND()*("14/01/2016"-"14/01/2010"+1))+"14/01/2010"</f>
-        <v>#VALUE!</v>
+        <v>40656.448822177095</v>
       </c>
     </row>
     <row r="391" spans="1:12" x14ac:dyDescent="0.3">
@@ -15795,9 +15809,9 @@
       <c r="K391" t="s">
         <v>17</v>
       </c>
-      <c r="L391" s="2" t="e">
+      <c r="L391" s="2">
         <f ca="1">(RAND()*("14/01/2016"-"14/01/2010"+1))+"14/01/2010"</f>
-        <v>#VALUE!</v>
+        <v>42175.912233500858</v>
       </c>
     </row>
   </sheetData>
